--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55EA2D2-F129-4599-BEF9-86491C3BF879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71363FA8-A07C-445C-9774-F23A4F769249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15795" yWindow="1065" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10935" yWindow="405" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>Sound/Voice_Pug_1_I_WantToEatPizza</t>
   </si>
@@ -68,6 +68,28 @@
   </si>
   <si>
     <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>챕터6 대사1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터6 대사2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터6 대사3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter01_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter01_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_3</t>
   </si>
 </sst>
 </file>
@@ -483,29 +505,45 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="G4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71363FA8-A07C-445C-9774-F23A4F769249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F50759A-9B27-46F1-A13F-F82527737BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10935" yWindow="405" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5235" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Sound/Voice_Pug_1_I_WantToEatPizza</t>
   </si>
@@ -40,16 +40,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>아무 대답하지 않는다,대답한다</t>
-  </si>
-  <si>
     <t>SelectionNameList</t>
   </si>
   <si>
     <t>NextDialogueId</t>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</t>
   </si>
   <si>
     <t>Id</t>
@@ -442,7 +436,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -454,16 +448,16 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
@@ -472,30 +466,30 @@
         <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>4</v>
@@ -506,14 +500,14 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>1</v>
@@ -522,14 +516,14 @@
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -538,11 +532,11 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -557,12 +551,8 @@
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
@@ -584,9 +574,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F50759A-9B27-46F1-A13F-F82527737BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7F7F4A-33C6-4315-B0F6-A300FEB24F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12240" yWindow="225" windowWidth="22275" windowHeight="15690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
-    <t>Sound/Voice_Pug_1_I_WantToEatPizza</t>
-  </si>
-  <si>
-    <t>Texture2D/Texture2D_Loading_1</t>
-  </si>
-  <si>
     <t>string[]</t>
   </si>
   <si>
@@ -62,18 +56,6 @@
   </si>
   <si>
     <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>챕터6 대사1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터6 대사2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터6 대사3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>dialogue_chapter01_1</t>
@@ -84,6 +66,26 @@
   </si>
   <si>
     <t>dialogue_chapter01_3</t>
+  </si>
+  <si>
+    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Basic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>훗, 가소로운 인간들. 이 정도로 날 막을 수 있을거라고 생각했나. 아직 몸도 안풀렸는데</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재미없는 싸움이었다. 지금은 이 정도로 마무리해주지.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>놈들의 비명은 시끄럽기만 할 뿐, 가치가 없다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -431,12 +433,13 @@
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="6" width="77.140625" customWidth="1"/>
-    <col min="7" max="8" width="50.7109375" customWidth="1"/>
+    <col min="7" max="7" width="57" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -448,103 +451,103 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7F7F4A-33C6-4315-B0F6-A300FEB24F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6B371A-3158-41A5-B65C-A100F0907DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12240" yWindow="225" windowWidth="22275" windowHeight="15690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="0" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="303">
   <si>
     <t>string[]</t>
   </si>
@@ -28,63 +28,1239 @@
     <t>VoicePath</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SelectionNameList</t>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>CharacterDataId</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(name)</t>
+  </si>
+  <si>
+    <t>고유 ID</t>
+  </si>
+  <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter01_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_3</t>
+  </si>
+  <si>
+    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Basic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Smile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter02_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter02_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter02_3</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter02_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter02_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter02_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter03_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_3</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter04_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_3</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter05_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_3</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter06_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_3</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter07_2</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_3</t>
+  </si>
+  <si>
+    <t>...여기가 지구인가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>생명 반응은 많지만... 너무 약하군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>꺄아악!! 괴물이야!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 정도 수준으로 나를 막겠다고?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구 정복... 생각보다 금방 끝나겠군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표 발견! 사격 개시!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>놈을 여기서 끝내야 한다!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번엔 조금 힘을 들였군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 안 죽는 거야...!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>의지는 인정해주지.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 약한 건 변함없다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 행성의 주인은 내가 될 것이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter02_7</t>
+  </si>
+  <si>
+    <t>부대 전진! 포격으로 밀어버려!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>드디어 장난감다운 걸 들고 나왔군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[거대한 폭발]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내겐 고작 조그마한 상처 하나 뿐이군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>말도 안돼… 전차 포격을 버텼다고?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 행성의 기술력, 생각보다 재미있군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter03_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_8</t>
+  </si>
+  <si>
+    <t>일반 병력으로는 상대 불가.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실험체 투입 허가 요청.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>허가한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정체불명의 인간들이 등장]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 놈들과는 움직임이 다르다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>제거 대상 확인.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>큭...!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 따위가… 날 밀어붙인다고?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 확보 완료.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터...?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대체 무슨 소리지?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter04_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_8</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_9</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_10</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_11</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_12</t>
+  </si>
+  <si>
+    <t>프로젝트 진행률 83% 돌파.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실험체 반응 수치 상승 중입니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…이 시설.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔가 익숙한데…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[어딘가에서 들려오는 음성]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>적합률이 부족하다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 단계로 넘어간다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누구냐!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[심한 두통]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리가… 크윽</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>놈이 기억하기 시작하는 거 같습니다..!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럴리가!! 봉인 상태는 유지되고 있습니다..!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…기억? 봉인? 이게 무슨소리야..!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter05_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_8</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_9</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_10</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_11</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_12</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_13</t>
+  </si>
+  <si>
+    <t>드디어 찾았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…뭐지? 너도 외계 생명체인가?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>외계인?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하… 정말 아무것도 모르는군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무슨 뜻이지.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 침략자가 아니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…무슨 소리지?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 만들어진 존재일 뿐. 아무것도 아니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>닥쳐!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>불쌍하군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 실험체의 불과해. 곧 '그것'이 완성될 것이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것…?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>진짜 지구 종말 프로젝트를…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[통신 종료]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대체 뭐라는 거야!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>크윽.. 머리속이 복잡해</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter06_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_8</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_9</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_10</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_11</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_12</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_13</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_14</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_15</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_16</t>
+  </si>
+  <si>
+    <t>실험체 E-01, 결국 여기까지 왔군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-01?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그게 네 진짜 이름이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>난… 지구를 정복하러 온…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 인간에게 만들어진 병기일 뿐이야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…거짓말</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">우리는 인류 멸망급 병기를 만들고 있다. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만 넌 실패작이야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패…?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 불완전했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래서 네 전투 데이터를 이용해 완벽한 존재를 완성해냈다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[거대한 문이 열린다]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…전투 개시.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>저건…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>완벽한 지구 종말 프로젝트.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 실패작은 곧 폐기된다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter07_4</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_5</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_8</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_9</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_10</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_11</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_12</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_13</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_14</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_15</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_16</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_17</t>
+  </si>
+  <si>
+    <t>Dialogue_Image/Citizen/Citizen_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>TexturePath</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>SelectionNameList</t>
-  </si>
-  <si>
-    <t>NextDialogueId</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>CharacterDataId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyTexturePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Police/Police_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Soldier1/Soldier1_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Soldier2/Soldier2_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Commander/Commander_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Agent/Agent_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Unknown/Unknown_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>...뭐지?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>...하지만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>...호오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Surprised</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_Image/Researcher1/Researcher1_0</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_Image/Alien_Silhouette/Alien_Silhouette_0</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_Image/Alien/Alien_0</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_Image/Kain/Kain_0</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_Image/Eclipse/Eclipse_0</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>고유 ID</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>dialogue_chapter01_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter01_2</t>
-  </si>
-  <si>
-    <t>dialogue_chapter01_3</t>
-  </si>
-  <si>
-    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Basic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue_Image/Dialogue_Image1/Dialogue_Image1_Smile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>훗, 가소로운 인간들. 이 정도로 날 막을 수 있을거라고 생각했나. 아직 몸도 안풀렸는데</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>재미없는 싸움이었다. 지금은 이 정도로 마무리해주지.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>놈들의 비명은 시끄럽기만 할 뿐, 가치가 없다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeakerName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔리스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시민</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경찰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>군인1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>군인2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지휘관</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수요원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>???</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>??</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter06_17</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_18</t>
+  </si>
+  <si>
+    <t>나는 관찰자다…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>관찰자?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>관찰자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카인</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형체</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형체</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project.이클립스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Dialogue_Image2/Dialogue_Image2_Angry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Researcher2/Researcher2_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>막아! 시민들을 대피시켜!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_final_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_final_2</t>
+  </si>
+  <si>
+    <t>dialogue_final_3</t>
+  </si>
+  <si>
+    <t>dialogue_final_4</t>
+  </si>
+  <si>
+    <t>dialogue_final_5</t>
+  </si>
+  <si>
+    <t>dialogue_final_6</t>
+  </si>
+  <si>
+    <t>dialogue_final_7</t>
+  </si>
+  <si>
+    <t>dialogue_final_8</t>
+  </si>
+  <si>
+    <t>dialogue_final_9</t>
+  </si>
+  <si>
+    <t>dialogue_final_10</t>
+  </si>
+  <si>
+    <t>dialogue_final_11</t>
+  </si>
+  <si>
+    <t>dialogue_final_12</t>
+  </si>
+  <si>
+    <t>dialogue_final_13</t>
+  </si>
+  <si>
+    <t>dialogue_final_14</t>
+  </si>
+  <si>
+    <t>…오류… 발생…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…전투.. 불가능…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[이클립스가 붕괴하기 시작한다]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…끝 인가?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하..하하…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>설마… 이클립스를 쓰러뜨릴줄은…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 나를 만들었지?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류는 두려웠다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>언젠가 찾아올 지구의 멸망을…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔리스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카인</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래서 신을 만들려 했다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…신?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 생명을 압도할 절대 신.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것이 지구 종말 프로젝트다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래서…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 머릿속에 지구를 정복하라는 명령을 심은 건가?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래야 신이 완성되니까.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…난 인간이었나?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한때는… 그랬지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정적]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…이름은</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>…..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시온.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시온..?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[희미하게 스쳐가는 기억]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>난… 죽었었군.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우린 널 되살렸다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류를 위한… 신으로.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류를 위해..?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수많은 인간을 죽였는데?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직도 깨닫지 못했군</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 나은 인류를 위해선 희생이 필요했다는 걸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 넌 선택해야 할거다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인류의 신이 될지.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니면…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>진정한 종말 그 자체가 될지.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[연구소 붕괴 경고]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[자폭 시퀀스 작동]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천장이 무너지기 시작했다]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴물.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_final_15</t>
+  </si>
+  <si>
+    <t>dialogue_final_16</t>
+  </si>
+  <si>
+    <t>dialogue_final_17</t>
+  </si>
+  <si>
+    <t>dialogue_final_18</t>
+  </si>
+  <si>
+    <t>dialogue_final_19</t>
+  </si>
+  <si>
+    <t>dialogue_final_20</t>
+  </si>
+  <si>
+    <t>dialogue_final_21</t>
+  </si>
+  <si>
+    <t>dialogue_final_22</t>
+  </si>
+  <si>
+    <t>dialogue_final_23</t>
+  </si>
+  <si>
+    <t>dialogue_final_24</t>
+  </si>
+  <si>
+    <t>dialogue_final_25</t>
+  </si>
+  <si>
+    <t>dialogue_final_26</t>
+  </si>
+  <si>
+    <t>dialogue_final_27</t>
+  </si>
+  <si>
+    <t>dialogue_final_28</t>
+  </si>
+  <si>
+    <t>dialogue_final_29</t>
+  </si>
+  <si>
+    <t>dialogue_final_30</t>
+  </si>
+  <si>
+    <t>dialogue_final_31</t>
+  </si>
+  <si>
+    <t>dialogue_final_32</t>
+  </si>
+  <si>
+    <t>dialogue_final_33</t>
+  </si>
+  <si>
+    <t>dialogue_final_34</t>
+  </si>
+  <si>
+    <t>dialogue_final_35</t>
+  </si>
+  <si>
+    <t>dialogue_final_36</t>
+  </si>
+  <si>
+    <t>dialogue_final_37</t>
+  </si>
+  <si>
+    <t>dialogue_final_38</t>
+  </si>
+  <si>
+    <t>dialogue_final_39</t>
+  </si>
+  <si>
+    <t>dialogue_final_40</t>
+  </si>
+  <si>
+    <t>dialogue_final_41</t>
+  </si>
+  <si>
+    <t>dialogue_final_42</t>
+  </si>
+  <si>
+    <t>dialogue_final_43</t>
+  </si>
+  <si>
+    <t>dialogue_final_44</t>
+  </si>
+  <si>
+    <t>dialogue_final_45</t>
+  </si>
+  <si>
+    <t>[거대한 폭발이 일어난다]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>난 대체 뭐였던 거지...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시온</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/Kain_Ending/Kain_Ending_0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -92,7 +1268,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -115,6 +1291,40 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -157,7 +1367,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -180,13 +1390,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -209,6 +1473,42 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -427,19 +1727,23 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:J1097"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="6" width="77.140625" customWidth="1"/>
-    <col min="7" max="7" width="57" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="77.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" customWidth="1"/>
+    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+    <col min="8" max="9" width="57" customWidth="1"/>
+    <col min="10" max="10" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -448,19 +1752,21 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
@@ -469,485 +1775,2798 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>186</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="G5" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="G6" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="5"/>
+      <c r="I7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
+      <c r="G12" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="23"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="J37" s="7"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J38" s="7"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42" s="7"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="7"/>
+      <c r="C43" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J43" s="7"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+    </row>
+    <row r="45" spans="1:10" s="20" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+    </row>
+    <row r="46" spans="1:10" s="20" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+    </row>
+    <row r="47" spans="1:10" s="20" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A47" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" s="16"/>
+      <c r="C47" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:10" s="20" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="J48" s="16"/>
+    </row>
+    <row r="49" spans="1:10" s="20" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="16"/>
+      <c r="C49" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="H50" s="7"/>
+      <c r="I50" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="J50" s="7"/>
+    </row>
+    <row r="51" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+    </row>
+    <row r="52" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="7"/>
+      <c r="C52" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="H52" s="7"/>
+      <c r="I52" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="J52" s="7"/>
+    </row>
+    <row r="53" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="7"/>
+      <c r="C53" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H53" s="7"/>
+      <c r="I53" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J53" s="7"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="16"/>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J55" s="7"/>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A56" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J57" s="7"/>
+    </row>
+    <row r="58" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A58" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+    </row>
+    <row r="59" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A59" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J59" s="7"/>
+    </row>
+    <row r="60" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A60" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A61" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J61" s="7"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A62" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J62" s="7"/>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A63" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A64" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="J64" s="7"/>
+    </row>
+    <row r="65" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A65" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+    </row>
+    <row r="66" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A66" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="7"/>
+      <c r="C66" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+    </row>
+    <row r="67" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A67" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+    </row>
+    <row r="68" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A68" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="7"/>
+      <c r="C68" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H68" s="7"/>
+      <c r="I68" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J68" s="7"/>
+    </row>
+    <row r="69" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A69" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="C69" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+    </row>
+    <row r="70" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A70" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J70" s="7"/>
+    </row>
+    <row r="71" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A71" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="7"/>
+      <c r="C71" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+    </row>
+    <row r="72" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A72" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" s="8"/>
+      <c r="C72" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="H72" s="8"/>
+      <c r="I72" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A73" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="8"/>
+      <c r="C73" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="H73" s="8"/>
+      <c r="I73" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B74" s="8"/>
+      <c r="C74" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A75" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="H75" s="8"/>
+      <c r="I75" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="8"/>
+      <c r="C76" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="H76" s="8"/>
+      <c r="I76" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A77" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B77" s="8"/>
+      <c r="C77" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="H78" s="9"/>
+      <c r="I78" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J78" s="9"/>
+    </row>
+    <row r="79" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A79" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="H79" s="9"/>
+      <c r="I79" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J79" s="9"/>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A80" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
+    </row>
+    <row r="81" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A81" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="H81" s="9"/>
+      <c r="I81" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="J81" s="9"/>
+    </row>
+    <row r="82" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="9"/>
+      <c r="C82" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+    </row>
+    <row r="83" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A83" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="9"/>
+      <c r="C83" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="H83" s="9"/>
+      <c r="I83" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J83" s="9"/>
+    </row>
+    <row r="84" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A84" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" s="9"/>
+      <c r="C84" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="H84" s="9"/>
+      <c r="I84" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J84" s="9"/>
+    </row>
+    <row r="85" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A85" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="29"/>
+      <c r="C85" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="H85" s="9"/>
+      <c r="I85" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="J85" s="9"/>
+    </row>
+    <row r="86" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A86" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" s="29"/>
+      <c r="C86" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="H86" s="9"/>
+      <c r="I86" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="J86" s="9"/>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A87" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B87" s="29"/>
+      <c r="C87" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="9"/>
+      <c r="I87" s="16"/>
+      <c r="J87" s="9"/>
+    </row>
+    <row r="88" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A88" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B88" s="29"/>
+      <c r="C88" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I88" s="16"/>
+      <c r="J88" s="9"/>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A89" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" s="29"/>
+      <c r="C89" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H89" s="9"/>
+      <c r="I89" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J89" s="9"/>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A90" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" s="29"/>
+      <c r="C90" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H90" s="9"/>
+      <c r="I90" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J90" s="9"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A91" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B91" s="29"/>
+      <c r="C91" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I91" s="16"/>
+      <c r="J91" s="9"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B92" s="29"/>
+      <c r="C92" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" s="16"/>
+      <c r="J92" s="9"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="29"/>
+      <c r="C93" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H93" s="9"/>
+      <c r="I93" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J93" s="9"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A94" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B94" s="29"/>
+      <c r="C94" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H94" s="9"/>
+      <c r="I94" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J94" s="9"/>
+    </row>
+    <row r="95" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A95" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B95" s="29"/>
+      <c r="C95" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H95" s="9"/>
+      <c r="I95" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J95" s="9"/>
+    </row>
+    <row r="96" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A96" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" s="29"/>
+      <c r="C96" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I96" s="16"/>
+      <c r="J96" s="9"/>
+    </row>
+    <row r="97" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A97" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B97" s="29"/>
+      <c r="C97" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H97" s="9"/>
+      <c r="I97" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J97" s="9"/>
+    </row>
+    <row r="98" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A98" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B98" s="29"/>
+      <c r="C98" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H98" s="9"/>
+      <c r="I98" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J98" s="9"/>
+    </row>
+    <row r="99" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A99" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B99" s="29"/>
+      <c r="C99" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" s="16"/>
+      <c r="J99" s="9"/>
+    </row>
+    <row r="100" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A100" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B100" s="29"/>
+      <c r="C100" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="16"/>
+      <c r="J100" s="9"/>
+    </row>
+    <row r="101" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A101" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B101" s="29"/>
+      <c r="C101" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H101" s="9"/>
+      <c r="I101" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J101" s="9"/>
+    </row>
+    <row r="102" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A102" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B102" s="29"/>
+      <c r="C102" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" s="16"/>
+      <c r="J102" s="9"/>
+    </row>
+    <row r="103" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A103" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B103" s="29"/>
+      <c r="C103" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H103" s="9"/>
+      <c r="I103" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J103" s="9"/>
+    </row>
+    <row r="104" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A104" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" s="29"/>
+      <c r="C104" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="9"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="9"/>
+    </row>
+    <row r="105" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A105" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B105" s="29"/>
+      <c r="C105" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="16"/>
+      <c r="J105" s="9"/>
+    </row>
+    <row r="106" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A106" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B106" s="29"/>
+      <c r="C106" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H106" s="9"/>
+      <c r="I106" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J106" s="9"/>
+    </row>
+    <row r="107" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A107" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B107" s="29"/>
+      <c r="C107" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H107" s="9"/>
+      <c r="I107" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J107" s="9"/>
+    </row>
+    <row r="108" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A108" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B108" s="29"/>
+      <c r="C108" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I108" s="16"/>
+      <c r="J108" s="9"/>
+    </row>
+    <row r="109" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A109" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B109" s="29"/>
+      <c r="C109" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="9"/>
+      <c r="I109" s="16"/>
+      <c r="J109" s="9"/>
+    </row>
+    <row r="110" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A110" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B110" s="29"/>
+      <c r="C110" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I110" s="16"/>
+      <c r="J110" s="9"/>
+    </row>
+    <row r="111" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A111" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B111" s="29"/>
+      <c r="C111" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" s="16"/>
+      <c r="J111" s="9"/>
+    </row>
+    <row r="112" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A112" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B112" s="29"/>
+      <c r="C112" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H112" s="9"/>
+      <c r="I112" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J112" s="9"/>
+    </row>
+    <row r="113" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A113" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B113" s="29"/>
+      <c r="C113" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H113" s="9"/>
+      <c r="I113" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J113" s="9"/>
+    </row>
+    <row r="114" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A114" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B114" s="29"/>
+      <c r="C114" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I114" s="16"/>
+      <c r="J114" s="9"/>
+    </row>
+    <row r="115" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A115" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B115" s="29"/>
+      <c r="C115" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E115" s="9"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I115" s="16"/>
+      <c r="J115" s="9"/>
+    </row>
+    <row r="116" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A116" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B116" s="29"/>
+      <c r="C116" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H116" s="9"/>
+      <c r="I116" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J116" s="9"/>
+    </row>
+    <row r="117" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A117" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B117" s="29"/>
+      <c r="C117" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H117" s="9"/>
+      <c r="I117" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J117" s="9"/>
+    </row>
+    <row r="118" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A118" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B118" s="29"/>
+      <c r="C118" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="16"/>
+      <c r="J118" s="9"/>
+    </row>
+    <row r="119" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A119" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B119" s="29"/>
+      <c r="C119" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E119" s="9"/>
+      <c r="F119" s="9"/>
+      <c r="G119" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H119" s="9"/>
+      <c r="I119" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J119" s="9"/>
+    </row>
+    <row r="120" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A120" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B120" s="29"/>
+      <c r="C120" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E120" s="9"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H120" s="9"/>
+      <c r="I120" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J120" s="9"/>
+    </row>
+    <row r="121" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A121" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B121" s="29"/>
+      <c r="C121" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H121" s="9"/>
+      <c r="I121" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J121" s="9"/>
+    </row>
+    <row r="122" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A122" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B122" s="29"/>
+      <c r="C122" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E122" s="9"/>
+      <c r="F122" s="9"/>
+      <c r="G122" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H122" s="9"/>
+      <c r="I122" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J122" s="9"/>
+    </row>
+    <row r="123" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A123" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B123" s="29"/>
+      <c r="C123" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="28"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="16"/>
+      <c r="J123" s="9"/>
+    </row>
+    <row r="124" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A124" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B124" s="29"/>
+      <c r="C124" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E124" s="9"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="28"/>
+      <c r="H124" s="9"/>
+      <c r="I124" s="16"/>
+      <c r="J124" s="9"/>
+    </row>
+    <row r="125" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A125" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B125" s="29"/>
+      <c r="C125" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" s="16"/>
+      <c r="J125" s="9"/>
+    </row>
+    <row r="126" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A126" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B126" s="29"/>
+      <c r="C126" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E126" s="9"/>
+      <c r="F126" s="9"/>
+      <c r="G126" s="28"/>
+      <c r="H126" s="9"/>
+      <c r="I126" s="16"/>
+      <c r="J126" s="9"/>
+    </row>
+    <row r="127" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A127" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B127" s="29"/>
+      <c r="C127" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I127" s="16"/>
+      <c r="J127" s="9"/>
+    </row>
+    <row r="128" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A128" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B128" s="29"/>
+      <c r="C128" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E128" s="9"/>
+      <c r="F128" s="9"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="9"/>
+      <c r="I128" s="16"/>
+      <c r="J128" s="9"/>
+    </row>
+    <row r="129" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A129" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B129" s="29"/>
+      <c r="C129" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="D129" s="30"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H129" s="9"/>
+      <c r="I129" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="J129" s="9"/>
+    </row>
+    <row r="130" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A130" s="3"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="32"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="28"/>
+      <c r="H130" s="9"/>
+      <c r="I130" s="16"/>
+      <c r="J130" s="9"/>
+    </row>
+    <row r="131" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A131" s="3"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="32"/>
+      <c r="D131" s="30"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="28"/>
+      <c r="H131" s="9"/>
+      <c r="I131" s="16"/>
+      <c r="J131" s="9"/>
+    </row>
+    <row r="132" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A132" s="9"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="33"/>
+      <c r="D132" s="30"/>
+      <c r="E132" s="9"/>
+      <c r="F132" s="9"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="9"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="9"/>
+    </row>
+    <row r="133" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="134" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="135" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="136" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="137" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="138" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="139" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="140" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="141" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="142" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="143" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="144" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
     <row r="147" ht="15.75" customHeight="1"/>
@@ -1804,6 +5423,103 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
+    <row r="1031" ht="15.75" customHeight="1"/>
+    <row r="1032" ht="15.75" customHeight="1"/>
+    <row r="1033" ht="15.75" customHeight="1"/>
+    <row r="1034" ht="15.75" customHeight="1"/>
+    <row r="1035" ht="15.75" customHeight="1"/>
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1"/>
+    <row r="1038" ht="15.75" customHeight="1"/>
+    <row r="1039" ht="15.75" customHeight="1"/>
+    <row r="1040" ht="15.75" customHeight="1"/>
+    <row r="1041" ht="15.75" customHeight="1"/>
+    <row r="1042" ht="15.75" customHeight="1"/>
+    <row r="1043" ht="15.75" customHeight="1"/>
+    <row r="1044" ht="15.75" customHeight="1"/>
+    <row r="1045" ht="15.75" customHeight="1"/>
+    <row r="1046" ht="15.75" customHeight="1"/>
+    <row r="1047" ht="15.75" customHeight="1"/>
+    <row r="1048" ht="15.75" customHeight="1"/>
+    <row r="1049" ht="15.75" customHeight="1"/>
+    <row r="1050" ht="15.75" customHeight="1"/>
+    <row r="1051" ht="15.75" customHeight="1"/>
+    <row r="1052" ht="15.75" customHeight="1"/>
+    <row r="1053" ht="15.75" customHeight="1"/>
+    <row r="1054" ht="15.75" customHeight="1"/>
+    <row r="1055" ht="15.75" customHeight="1"/>
+    <row r="1056" ht="15.75" customHeight="1"/>
+    <row r="1057" ht="15.75" customHeight="1"/>
+    <row r="1058" ht="15.75" customHeight="1"/>
+    <row r="1059" ht="15.75" customHeight="1"/>
+    <row r="1060" ht="15.75" customHeight="1"/>
+    <row r="1061" ht="15.75" customHeight="1"/>
+    <row r="1062" ht="15.75" customHeight="1"/>
+    <row r="1063" ht="15.75" customHeight="1"/>
+    <row r="1064" ht="15.75" customHeight="1"/>
+    <row r="1065" ht="15.75" customHeight="1"/>
+    <row r="1066" ht="15.75" customHeight="1"/>
+    <row r="1067" ht="15.75" customHeight="1"/>
+    <row r="1068" ht="15.75" customHeight="1"/>
+    <row r="1069" ht="15.75" customHeight="1"/>
+    <row r="1070" ht="15.75" customHeight="1"/>
+    <row r="1071" ht="15.75" customHeight="1"/>
+    <row r="1072" ht="15.75" customHeight="1"/>
+    <row r="1073" ht="15.75" customHeight="1"/>
+    <row r="1074" ht="15.75" customHeight="1"/>
+    <row r="1075" ht="15.75" customHeight="1"/>
+    <row r="1076" ht="15.75" customHeight="1"/>
+    <row r="1077" ht="15.75" customHeight="1"/>
+    <row r="1078" ht="15.75" customHeight="1"/>
+    <row r="1079" ht="15.75" customHeight="1"/>
+    <row r="1080" ht="15.75" customHeight="1"/>
+    <row r="1081" ht="15.75" customHeight="1"/>
+    <row r="1082" ht="15.75" customHeight="1"/>
+    <row r="1083" ht="15.75" customHeight="1"/>
+    <row r="1084" ht="15.75" customHeight="1"/>
+    <row r="1085" ht="15.75" customHeight="1"/>
+    <row r="1086" ht="15.75" customHeight="1"/>
+    <row r="1087" ht="15.75" customHeight="1"/>
+    <row r="1088" ht="15.75" customHeight="1"/>
+    <row r="1089" ht="15.75" customHeight="1"/>
+    <row r="1090" ht="15.75" customHeight="1"/>
+    <row r="1091" ht="15.75" customHeight="1"/>
+    <row r="1092" ht="15.75" customHeight="1"/>
+    <row r="1093" ht="15.75" customHeight="1"/>
+    <row r="1094" ht="15.75" customHeight="1"/>
+    <row r="1095" ht="15.75" customHeight="1"/>
+    <row r="1096" ht="15.75" customHeight="1"/>
+    <row r="1097" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6B371A-3158-41A5-B65C-A100F0907DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50F7D7D-594D-4EA5-9D62-E8A762B6FC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="0" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="0" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="301">
   <si>
     <t>string[]</t>
   </si>
@@ -501,26 +501,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>E-01?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>그게 네 진짜 이름이다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>난… 지구를 정복하러 온…</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아니.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>너는 인간에게 만들어진 병기일 뿐이야.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>…거짓말</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -534,10 +514,6 @@
   </si>
   <si>
     <t>실패…?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>너는 불완전했다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1023,10 +999,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>솔리스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>카인</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1079,14 +1051,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>시온.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>시온..?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>[희미하게 스쳐가는 기억]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1256,11 +1220,39 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>시온</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Dialogue_Image/Kain_Ending/Kain_Ending_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔리스…?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>넌 누구냐!!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>난 널 만들어낸 존재이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>날 만들었다고?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 이름은 카인… 너는 내 손으로 만들어졌다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 너는 내가 만들어낸 병기일 뿐이야.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 불완전하다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1450,7 +1442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1509,6 +1501,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1775,13 +1768,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>7</v>
@@ -1807,13 +1800,13 @@
         <v>10</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>1</v>
@@ -1831,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
@@ -1853,7 +1846,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
@@ -1875,10 +1868,10 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="22" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1888,7 +1881,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="11" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>20</v>
@@ -1896,11 +1889,11 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1918,7 +1911,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>15</v>
@@ -1938,7 +1931,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>15</v>
@@ -1960,11 +1953,11 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -1982,11 +1975,11 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J11" s="5"/>
     </row>
@@ -2004,7 +1997,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
@@ -2026,11 +2019,11 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -2048,7 +2041,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>15</v>
@@ -2070,7 +2063,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>14</v>
@@ -2090,7 +2083,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>14</v>
@@ -2112,11 +2105,11 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2126,7 +2119,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>27</v>
@@ -2134,7 +2127,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>14</v>
@@ -2156,7 +2149,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>15</v>
@@ -2196,7 +2189,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -2218,11 +2211,11 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="J22" s="5"/>
     </row>
@@ -2232,7 +2225,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>63</v>
@@ -2240,7 +2233,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>14</v>
@@ -2260,7 +2253,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>15</v>
@@ -2282,11 +2275,11 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3"/>
     </row>
@@ -2304,11 +2297,11 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J26" s="6"/>
     </row>
@@ -2326,11 +2319,11 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J27" s="6"/>
     </row>
@@ -2357,7 +2350,7 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>77</v>
@@ -2365,10 +2358,10 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
@@ -2387,10 +2380,10 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
@@ -2409,11 +2402,11 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J31" s="6"/>
     </row>
@@ -2431,10 +2424,10 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
@@ -2453,10 +2446,10 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
@@ -2475,11 +2468,11 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J34" s="6"/>
     </row>
@@ -2497,10 +2490,10 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -2517,7 +2510,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>14</v>
@@ -2539,11 +2532,11 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="25" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="16" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J37" s="7"/>
     </row>
@@ -2561,11 +2554,11 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="25" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="16" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J38" s="7"/>
     </row>
@@ -2583,7 +2576,7 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>14</v>
@@ -2605,7 +2598,7 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>14</v>
@@ -2645,11 +2638,11 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="16" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J42" s="7"/>
     </row>
@@ -2667,11 +2660,11 @@
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="16" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J43" s="7"/>
     </row>
@@ -2689,10 +2682,10 @@
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
@@ -2729,10 +2722,10 @@
       <c r="E46" s="16"/>
       <c r="F46" s="16"/>
       <c r="G46" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="16"/>
@@ -2751,11 +2744,11 @@
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
       <c r="G47" s="25" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H47" s="16"/>
       <c r="I47" s="16" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J47" s="16"/>
     </row>
@@ -2773,11 +2766,11 @@
       <c r="E48" s="16"/>
       <c r="F48" s="16"/>
       <c r="G48" s="25" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H48" s="16"/>
       <c r="I48" s="16" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J48" s="16"/>
     </row>
@@ -2793,7 +2786,7 @@
       <c r="E49" s="16"/>
       <c r="F49" s="16"/>
       <c r="G49" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>14</v>
@@ -2815,11 +2808,11 @@
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="25" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J50" s="7"/>
     </row>
@@ -2837,7 +2830,7 @@
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>14</v>
@@ -2859,11 +2852,11 @@
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="25" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H52" s="7"/>
       <c r="I52" s="16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J52" s="7"/>
     </row>
@@ -2873,7 +2866,7 @@
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>124</v>
@@ -2881,11 +2874,11 @@
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J53" s="7"/>
     </row>
@@ -2895,7 +2888,7 @@
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="17" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>125</v>
@@ -2903,7 +2896,7 @@
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>14</v>
@@ -2925,11 +2918,11 @@
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J55" s="7"/>
     </row>
@@ -2947,7 +2940,7 @@
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>14</v>
@@ -2969,11 +2962,11 @@
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J57" s="7"/>
     </row>
@@ -2991,7 +2984,7 @@
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>14</v>
@@ -3013,11 +3006,11 @@
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
       <c r="G59" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J59" s="7"/>
     </row>
@@ -3035,10 +3028,10 @@
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
@@ -3057,11 +3050,11 @@
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
       <c r="G61" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J61" s="7"/>
     </row>
@@ -3079,11 +3072,11 @@
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J62" s="7"/>
     </row>
@@ -3101,7 +3094,7 @@
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
       <c r="G63" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>14</v>
@@ -3123,11 +3116,11 @@
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
       <c r="G64" s="26" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J64" s="7"/>
     </row>
@@ -3140,7 +3133,7 @@
         <v>120</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
@@ -3151,29 +3144,29 @@
     </row>
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="17" t="s">
         <v>121</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
       <c r="G66" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B67" s="7"/>
       <c r="C67" s="17" t="s">
@@ -3183,10 +3176,10 @@
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
@@ -3205,11 +3198,11 @@
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="16" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J68" s="7"/>
     </row>
@@ -3219,7 +3212,7 @@
       </c>
       <c r="B69" s="7"/>
       <c r="C69" s="17" t="s">
-        <v>137</v>
+        <v>295</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>39</v>
@@ -3227,10 +3220,10 @@
       <c r="E69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
@@ -3241,37 +3234,37 @@
       </c>
       <c r="B70" s="7"/>
       <c r="C70" s="17" t="s">
-        <v>138</v>
+        <v>296</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
       <c r="G70" s="16" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H70" s="7"/>
       <c r="I70" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J70" s="7"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B71" s="7"/>
       <c r="C71" s="17" t="s">
-        <v>139</v>
+        <v>297</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
       <c r="G71" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>14</v>
@@ -3281,63 +3274,63 @@
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="18" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J72" s="8"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="18" t="s">
-        <v>141</v>
+        <v>299</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J73" s="8"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="18" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>14</v>
@@ -3347,63 +3340,63 @@
     </row>
     <row r="75" spans="1:10" ht="15.75" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="18" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
       <c r="G75" s="27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H75" s="8"/>
       <c r="I75" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J75" s="8"/>
     </row>
     <row r="76" spans="1:10" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H76" s="8"/>
       <c r="I76" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J76" s="8"/>
     </row>
     <row r="77" spans="1:10" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="18" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>14</v>
@@ -3413,58 +3406,58 @@
     </row>
     <row r="78" spans="1:10" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B78" s="9"/>
       <c r="C78" s="19" t="s">
-        <v>146</v>
+        <v>300</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
       <c r="G78" s="28" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J78" s="9"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B79" s="9"/>
       <c r="C79" s="19" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="28" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J79" s="9"/>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="19" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
@@ -3475,41 +3468,41 @@
     </row>
     <row r="81" spans="1:10" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B81" s="9"/>
       <c r="C81" s="19" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E81" s="9"/>
       <c r="F81" s="9"/>
       <c r="G81" s="28" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="21" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J81" s="9"/>
     </row>
     <row r="82" spans="1:10" ht="15.75" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B82" s="9"/>
       <c r="C82" s="19" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9"/>
       <c r="G82" s="24" t="s">
-        <v>188</v>
+        <v>293</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>14</v>
@@ -3519,100 +3512,100 @@
     </row>
     <row r="83" spans="1:10" ht="15.75" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B83" s="9"/>
       <c r="C83" s="19" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
       <c r="G83" s="28" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J83" s="9"/>
     </row>
     <row r="84" spans="1:10" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B84" s="9"/>
       <c r="C84" s="31" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
       <c r="G84" s="28" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J84" s="9"/>
     </row>
     <row r="85" spans="1:10" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B85" s="29"/>
       <c r="C85" s="32" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
       <c r="G85" s="28" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="21" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J85" s="9"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B86" s="29"/>
       <c r="C86" s="32" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
       <c r="G86" s="28" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="21" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J86" s="9"/>
     </row>
     <row r="87" spans="1:10" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B87" s="29"/>
       <c r="C87" s="32" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
@@ -3623,19 +3616,19 @@
     </row>
     <row r="88" spans="1:10" ht="15.75" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B88" s="29"/>
       <c r="C88" s="32" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
-      <c r="G88" s="28" t="s">
-        <v>235</v>
+      <c r="G88" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>14</v>
@@ -3645,63 +3638,63 @@
     </row>
     <row r="89" spans="1:10" ht="15.75" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B89" s="29"/>
       <c r="C89" s="32" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
       <c r="G89" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H89" s="9"/>
       <c r="I89" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J89" s="9"/>
     </row>
     <row r="90" spans="1:10" ht="15.75" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B90" s="29"/>
       <c r="C90" s="32" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
       <c r="G90" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J90" s="9"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B91" s="29"/>
       <c r="C91" s="32" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
-      <c r="G91" s="28" t="s">
-        <v>235</v>
+      <c r="G91" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>14</v>
@@ -3711,19 +3704,19 @@
     </row>
     <row r="92" spans="1:10" ht="15.75" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B92" s="29"/>
       <c r="C92" s="32" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9"/>
-      <c r="G92" s="28" t="s">
-        <v>235</v>
+      <c r="G92" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>14</v>
@@ -3733,151 +3726,151 @@
     </row>
     <row r="93" spans="1:10" ht="15.75" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B93" s="29"/>
       <c r="C93" s="32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
       <c r="G93" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H93" s="9"/>
       <c r="I93" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J93" s="9"/>
     </row>
     <row r="94" spans="1:10" ht="15.75" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B94" s="29"/>
       <c r="C94" s="32" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
       <c r="G94" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J94" s="9"/>
     </row>
     <row r="95" spans="1:10" ht="15.75" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B95" s="29"/>
       <c r="C95" s="32" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
       <c r="G95" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H95" s="9"/>
       <c r="I95" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J95" s="9"/>
     </row>
     <row r="96" spans="1:10" ht="15.75" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B96" s="29"/>
       <c r="C96" s="32" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
-      <c r="G96" s="28" t="s">
-        <v>235</v>
+      <c r="G96" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I96" s="16"/>
       <c r="J96" s="9"/>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B97" s="29"/>
       <c r="C97" s="32" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
       <c r="G97" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H97" s="9"/>
       <c r="I97" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J97" s="9"/>
     </row>
     <row r="98" spans="1:10" ht="15.75" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B98" s="29"/>
       <c r="C98" s="32" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
       <c r="G98" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J98" s="9"/>
     </row>
     <row r="99" spans="1:10" ht="15.75" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B99" s="29"/>
       <c r="C99" s="32" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
-      <c r="G99" s="28" t="s">
-        <v>235</v>
+      <c r="G99" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>14</v>
@@ -3887,19 +3880,19 @@
     </row>
     <row r="100" spans="1:10" ht="15.75" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B100" s="29"/>
       <c r="C100" s="32" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9"/>
-      <c r="G100" s="28" t="s">
-        <v>235</v>
+      <c r="G100" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>14</v>
@@ -3909,41 +3902,41 @@
     </row>
     <row r="101" spans="1:10" ht="15.75" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B101" s="29"/>
       <c r="C101" s="32" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
       <c r="G101" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H101" s="9"/>
       <c r="I101" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J101" s="9"/>
     </row>
     <row r="102" spans="1:10" ht="15.75" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B102" s="29"/>
       <c r="C102" s="32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9"/>
-      <c r="G102" s="28" t="s">
-        <v>235</v>
+      <c r="G102" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>14</v>
@@ -3953,36 +3946,36 @@
     </row>
     <row r="103" spans="1:10" ht="15.75" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B103" s="29"/>
       <c r="C103" s="32" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E103" s="9"/>
       <c r="F103" s="9"/>
       <c r="G103" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H103" s="9"/>
       <c r="I103" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J103" s="9"/>
     </row>
     <row r="104" spans="1:10" ht="15.75" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B104" s="29"/>
       <c r="C104" s="32" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
@@ -3993,19 +3986,19 @@
     </row>
     <row r="105" spans="1:10" ht="15.75" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B105" s="29"/>
       <c r="C105" s="32" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
-      <c r="G105" s="28" t="s">
-        <v>235</v>
+      <c r="G105" s="24" t="s">
+        <v>293</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>14</v>
@@ -4015,63 +4008,63 @@
     </row>
     <row r="106" spans="1:10" ht="15.75" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B106" s="29"/>
       <c r="C106" s="32" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
       <c r="G106" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H106" s="9"/>
       <c r="I106" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J106" s="9"/>
     </row>
     <row r="107" spans="1:10" ht="15.75" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B107" s="29"/>
       <c r="C107" s="32" t="s">
-        <v>249</v>
+        <v>182</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
       <c r="G107" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H107" s="9"/>
       <c r="I107" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J107" s="9"/>
     </row>
     <row r="108" spans="1:10" ht="15.75" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B108" s="29"/>
+        <v>268</v>
+      </c>
+      <c r="B108" s="34"/>
       <c r="C108" s="32" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E108" s="9"/>
       <c r="F108" s="9"/>
       <c r="G108" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>14</v>
@@ -4081,14 +4074,14 @@
     </row>
     <row r="109" spans="1:10" ht="15.75" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B109" s="29"/>
       <c r="C109" s="32" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E109" s="9"/>
       <c r="F109" s="9"/>
@@ -4099,19 +4092,19 @@
     </row>
     <row r="110" spans="1:10" ht="15.75" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B110" s="29"/>
       <c r="C110" s="32" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
       <c r="G110" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>14</v>
@@ -4121,19 +4114,19 @@
     </row>
     <row r="111" spans="1:10" ht="15.75" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B111" s="29"/>
       <c r="C111" s="32" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
       <c r="G111" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>14</v>
@@ -4143,151 +4136,151 @@
     </row>
     <row r="112" spans="1:10" ht="15.75" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B112" s="29"/>
       <c r="C112" s="32" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E112" s="9"/>
       <c r="F112" s="9"/>
       <c r="G112" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H112" s="9"/>
       <c r="I112" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J112" s="9"/>
     </row>
     <row r="113" spans="1:10" ht="15.75" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B113" s="29"/>
       <c r="C113" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E113" s="9"/>
       <c r="F113" s="9"/>
       <c r="G113" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H113" s="9"/>
       <c r="I113" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J113" s="9"/>
     </row>
     <row r="114" spans="1:10" ht="15.75" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B114" s="29"/>
       <c r="C114" s="32" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E114" s="9"/>
       <c r="F114" s="9"/>
       <c r="G114" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I114" s="16"/>
       <c r="J114" s="9"/>
     </row>
     <row r="115" spans="1:10" ht="15.75" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B115" s="29"/>
       <c r="C115" s="32" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
       <c r="G115" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I115" s="16"/>
       <c r="J115" s="9"/>
     </row>
     <row r="116" spans="1:10" ht="15.75" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B116" s="29"/>
       <c r="C116" s="32" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
       <c r="G116" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H116" s="9"/>
       <c r="I116" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J116" s="9"/>
     </row>
     <row r="117" spans="1:10" ht="15.75" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B117" s="29"/>
       <c r="C117" s="32" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
       <c r="G117" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H117" s="9"/>
       <c r="I117" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J117" s="9"/>
     </row>
     <row r="118" spans="1:10" ht="15.75" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B118" s="29"/>
       <c r="C118" s="32" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E118" s="9"/>
       <c r="F118" s="9"/>
       <c r="G118" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>14</v>
@@ -4297,102 +4290,102 @@
     </row>
     <row r="119" spans="1:10" ht="15.75" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B119" s="29"/>
       <c r="C119" s="32" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
       <c r="G119" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H119" s="9"/>
       <c r="I119" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J119" s="9"/>
     </row>
     <row r="120" spans="1:10" ht="15.75" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B120" s="29"/>
       <c r="C120" s="32" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E120" s="9"/>
       <c r="F120" s="9"/>
       <c r="G120" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H120" s="9"/>
       <c r="I120" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J120" s="9"/>
     </row>
     <row r="121" spans="1:10" ht="15.75" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B121" s="29"/>
       <c r="C121" s="32" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E121" s="9"/>
       <c r="F121" s="9"/>
       <c r="G121" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H121" s="9"/>
       <c r="I121" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J121" s="9"/>
     </row>
     <row r="122" spans="1:10" ht="15.75" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B122" s="29"/>
       <c r="C122" s="32" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E122" s="9"/>
       <c r="F122" s="9"/>
       <c r="G122" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H122" s="9"/>
       <c r="I122" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J122" s="9"/>
     </row>
     <row r="123" spans="1:10" ht="15.75" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B123" s="29"/>
       <c r="C123" s="32" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
@@ -4403,14 +4396,14 @@
     </row>
     <row r="124" spans="1:10" ht="15.75" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B124" s="29"/>
       <c r="C124" s="32" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E124" s="9"/>
       <c r="F124" s="9"/>
@@ -4421,19 +4414,19 @@
     </row>
     <row r="125" spans="1:10" ht="15.75" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B125" s="29"/>
       <c r="C125" s="32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E125" s="9"/>
       <c r="F125" s="9"/>
       <c r="G125" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>14</v>
@@ -4443,14 +4436,14 @@
     </row>
     <row r="126" spans="1:10" ht="15.75" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B126" s="29"/>
       <c r="C126" s="32" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E126" s="9"/>
       <c r="F126" s="9"/>
@@ -4461,19 +4454,19 @@
     </row>
     <row r="127" spans="1:10" ht="15.75" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B127" s="29"/>
       <c r="C127" s="32" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9"/>
       <c r="G127" s="28" t="s">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>14</v>
@@ -4483,14 +4476,14 @@
     </row>
     <row r="128" spans="1:10" ht="15.75" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B128" s="29"/>
       <c r="C128" s="32" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E128" s="9"/>
       <c r="F128" s="9"/>
@@ -4501,21 +4494,21 @@
     </row>
     <row r="129" spans="1:10" ht="15.75" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B129" s="29"/>
       <c r="C129" s="32" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="D129" s="30"/>
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
       <c r="G129" s="28" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H129" s="9"/>
       <c r="I129" s="16" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="J129" s="9"/>
     </row>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380D48A8-7402-458C-92EE-028C478D6CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
